--- a/HW2/HW2.xlsx
+++ b/HW2/HW2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Romeo\Git\ENPM818J\HW2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C38E82-3BD2-4089-90F7-772B51939D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724879E4-3782-4C59-95AD-CC9ED37A99CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42F42B02-E868-469F-B953-81B95CE14635}"/>
   </bookViews>
@@ -559,6 +559,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -584,45 +623,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -966,52 +966,52 @@
   <sheetData>
     <row r="2" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
     </row>
     <row r="4" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="51"/>
     </row>
     <row r="6" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="51"/>
     </row>
     <row r="7" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N8" s="31" t="s">
@@ -1031,18 +1031,18 @@
       </c>
     </row>
     <row r="9" spans="2:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="47"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="34"/>
       <c r="N9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1061,16 +1061,16 @@
       </c>
     </row>
     <row r="10" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="53"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="41"/>
       <c r="N10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1089,16 +1089,16 @@
       </c>
     </row>
     <row r="11" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="41"/>
       <c r="N11" s="2" t="s">
         <v>13</v>
       </c>
@@ -1117,28 +1117,28 @@
       </c>
     </row>
     <row r="12" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="53"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="41"/>
     </row>
     <row r="13" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="48"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="49"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="36"/>
     </row>
     <row r="16" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="7"/>
@@ -1364,76 +1364,76 @@
       <c r="D21" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="44" t="s">
+      <c r="G21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="45"/>
-      <c r="K21" s="44" t="s">
+      <c r="J21" s="44"/>
+      <c r="K21" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="44" t="s">
+      <c r="L21" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="M21" s="44" t="s">
+      <c r="M21" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="N21" s="44" t="s">
+      <c r="N21" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="O21" s="44" t="s">
+      <c r="O21" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="P21" s="42" t="s">
+      <c r="P21" s="45" t="s">
         <v>25</v>
       </c>
       <c r="Q21" s="43"/>
-      <c r="R21" s="44" t="s">
+      <c r="R21" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="S21" s="44" t="s">
+      <c r="S21" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="T21" s="44" t="s">
+      <c r="T21" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="U21" s="44" t="s">
+      <c r="U21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="V21" s="44" t="s">
+      <c r="V21" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="W21" s="44" t="s">
+      <c r="W21" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="X21" s="44" t="s">
+      <c r="X21" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="Y21" s="42" t="s">
+      <c r="Y21" s="45" t="s">
         <v>25</v>
       </c>
       <c r="Z21" s="43"/>
-      <c r="AA21" s="44" t="s">
+      <c r="AA21" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="AB21" s="44" t="s">
+      <c r="AB21" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="AC21" s="44" t="s">
+      <c r="AC21" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="AD21" s="42" t="s">
+      <c r="AD21" s="45" t="s">
         <v>33</v>
       </c>
       <c r="AF21" s="30"/>
@@ -1442,96 +1442,96 @@
     <row r="22" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C22" s="5"/>
       <c r="D22" s="43"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="42"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="45"/>
       <c r="Q22" s="43"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="44"/>
-      <c r="T22" s="44"/>
-      <c r="U22" s="44"/>
-      <c r="V22" s="44"/>
-      <c r="W22" s="44"/>
-      <c r="X22" s="44"/>
-      <c r="Y22" s="42"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="37"/>
+      <c r="Y22" s="45"/>
       <c r="Z22" s="43"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="42"/>
+      <c r="AA22" s="37"/>
+      <c r="AB22" s="37"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="45"/>
       <c r="AF22" s="30"/>
       <c r="AG22" s="30"/>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C23" s="5"/>
       <c r="D23" s="43"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="42"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="45"/>
       <c r="Q23" s="43"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44"/>
-      <c r="U23" s="44"/>
-      <c r="V23" s="44"/>
-      <c r="W23" s="44"/>
-      <c r="X23" s="44"/>
-      <c r="Y23" s="42"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="45"/>
       <c r="Z23" s="43"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
-      <c r="AC23" s="44"/>
-      <c r="AD23" s="42"/>
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="45"/>
       <c r="AF23" s="30"/>
       <c r="AG23" s="30"/>
     </row>
     <row r="24" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="4"/>
       <c r="D24" s="43"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="42"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="45"/>
       <c r="Q24" s="43"/>
-      <c r="R24" s="44"/>
-      <c r="S24" s="44"/>
-      <c r="T24" s="44"/>
-      <c r="U24" s="44"/>
-      <c r="V24" s="44"/>
-      <c r="W24" s="44"/>
-      <c r="X24" s="44"/>
-      <c r="Y24" s="42"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="45"/>
       <c r="Z24" s="43"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="44"/>
-      <c r="AC24" s="44"/>
-      <c r="AD24" s="42"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="45"/>
     </row>
     <row r="25" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
@@ -1550,28 +1550,27 @@
       </c>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="47"/>
+      <c r="C27" s="34"/>
     </row>
     <row r="28" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="48"/>
-      <c r="C28" s="49"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="B9:K13"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="V21:V24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="W21:W24"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="Y21:Z24"/>
+    <mergeCell ref="AD21:AD24"/>
+    <mergeCell ref="AA21:AA24"/>
+    <mergeCell ref="AB21:AB24"/>
+    <mergeCell ref="AC21:AC24"/>
     <mergeCell ref="X21:X24"/>
     <mergeCell ref="K21:K24"/>
     <mergeCell ref="L21:L24"/>
@@ -1583,16 +1582,17 @@
     <mergeCell ref="R21:R24"/>
     <mergeCell ref="M21:M24"/>
     <mergeCell ref="N21:N24"/>
-    <mergeCell ref="Y21:Z24"/>
-    <mergeCell ref="AD21:AD24"/>
-    <mergeCell ref="AA21:AA24"/>
-    <mergeCell ref="AB21:AB24"/>
-    <mergeCell ref="AC21:AC24"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="V21:V24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="W21:W24"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="B9:K13"/>
+    <mergeCell ref="D21:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
